--- a/BACENJUD.xlsx
+++ b/BACENJUD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC2"/>
+  <dimension ref="A1:BD2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,6 +693,11 @@
       </c>
       <c r="BC1" t="inlineStr">
         <is>
+          <t>FOI BAIXADO ANTES</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
           <t>Pasta</t>
         </is>
       </c>
@@ -775,7 +780,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Execução</t>
+          <t>Sentenciado</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -790,7 +795,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-02-27 00:00:00</t>
+          <t>2026-04-14 00:00:00</t>
         </is>
       </c>
       <c r="T2" s="1" t="n">
@@ -802,7 +807,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>6832844</v>
+        <v>68328.44</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
@@ -835,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>75781.89</v>
+        <v>77303.97</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -884,7 +889,7 @@
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>75781.89</v>
+        <v>77303.97</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -908,7 +913,7 @@
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3624424</v>
+        <v>36244.24</v>
       </c>
       <c r="AY2" t="n">
         <v>34660.26</v>
@@ -922,7 +927,12 @@
       <c r="BB2" t="n">
         <v>0</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
         <v>63247</v>
       </c>
     </row>

--- a/BACENJUD.xlsx
+++ b/BACENJUD.xlsx
@@ -705,37 +705,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5354256-46.2020.8.09.0051</t>
+          <t>1005073-61.2016.8.26.0361</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>projuris-63247</t>
+          <t>projuris-68143</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Tributário</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RAIANE LIMA GOMES MATOS</t>
+          <t>PREFEITURA DO MUNICIPIO DE MOGI DAS CRUZES</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ERBE INCORPORADORA 122 LTDA.</t>
+          <t>ANTARES PARTICIPAÇÕES LTDA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ENCERRADOS</t>
+          <t>BAIXA PROVISÓRIA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MASCARENHAS BARBOSA ADVOGADOS</t>
+          <t>REIS GONÇALVES BASTOS E HORA ADVOGADOS - RGBH</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -745,74 +745,80 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>JARDIM DO CERRADO FASE 5.1</t>
+          <t>REAL PARK TIETE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>RAIANE LIMA GOMES MATOS propôs ação de indenização por danos morais e materiais em face de TG CERRADO EMPREENDIMENTOS LTDA; narrou que adquiriu da requerida, por intermédio do programa minha casa minha vida, apartamento localizado no Conjunto Cerrado VII em Goiânia; contou que, desde a época em que o imóvel lhe foi entregue, vem apresentando problemas estruturais; entrou em contato com a construtora e relatou o problema por diversas vezes; foram realizados reparos que nunca surtiram o efeito desejado; pouco tempo depois o imóvel apresentava os mesmos problemas; requereu a condenação ao pagamento de R$ 27.963,97 a título de danos materiais, bem como pagamento de R$ 20.000,00, a título de danos morais.</t>
+          <t>Natureza: IPTU
+Localizacao do Imovel: Quadra: 40 Lote:06 Loteam/:6451 RESIDENCIAL REAL P
+Exercícios: 2013, 2014, 2015
+Incrição: 36.041.006.000
+Valor da Causa: R$ 14.937,06.
+OBS: Valor do provável condiz com o bloqueio que houve na conta bancária. Alinhado com o André.
+OBS: Alinhado com o André para não inserir requisição de ciência.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>FAR - Vício Construtivo Unidade Autônoma</t>
+          <t>IPTU Cliente</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>26ª Vara Cível - Goiânia, GO/TJGO</t>
+          <t>Vara da Fazenda Pública - Mogi das Cruzes, SP/TJSP</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Ordinário</t>
+          <t>Execução</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sentenciado</t>
+          <t>Execução</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Indenizatória</t>
+          <t>Execução Fiscal</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Procedência</t>
+          <t>Condenação paga - Aguardando baixa</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-04-14 00:00:00</t>
+          <t>2026-07-07 00:00:00</t>
         </is>
       </c>
       <c r="T2" s="1" t="n">
-        <v>44251</v>
+        <v>44988</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2020-07-21 00:00:00</t>
+          <t>2016-06-06 00:00:00</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>68328.44</v>
+        <v>20649.86</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Karina Cruz da Silva</t>
+          <t>Daniele Pereira Lima</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -822,16 +828,16 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2025-03-30 00:00:00</t>
+          <t>1900-01-01 00:00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>R$ 33.668,18</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>68328.44</v>
+        <v>20649.86</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -840,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>77303.97</v>
+        <v>33083.13</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -848,39 +854,31 @@
       <c r="AG2" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>ALVES &amp; NEVES ADVOCACIA</t>
-        </is>
-      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>6890.3</v>
+        <v>20649.82</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>ALVES &amp; NEVES ADVOCACIA</t>
-        </is>
-      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>026.210.441-58</t>
+          <t>46.523.270/0001-88</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>CPF/ME 026.210.441-58</t>
+          <t>CNPJ/ME 46.523.270/0001-88</t>
         </is>
       </c>
       <c r="AO2" t="n">
-        <v>47963.97</v>
+        <v>14937.06</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-07-07 00:00:00</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -889,11 +887,11 @@
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>77303.97</v>
+        <v>33083.13</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2026-06-30 00:00:00</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -902,10 +900,10 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>6890.3</v>
+        <v>20649.82</v>
       </c>
       <c r="AV2" t="n">
-        <v>7357.91</v>
+        <v>33592.02</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -913,13 +911,13 @@
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>36244.24</v>
+        <v>0.04</v>
       </c>
       <c r="AY2" t="n">
-        <v>34660.26</v>
+        <v>0.04</v>
       </c>
       <c r="AZ2" t="n">
-        <v>36244.24</v>
+        <v>0.04</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -929,11 +927,11 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>63247</v>
+        <v>68143</v>
       </c>
     </row>
   </sheetData>
